--- a/Decks/Zuko.xlsx
+++ b/Decks/Zuko.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD95EA2-3AA3-4620-82D4-2DF75A13DD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE768CB8-DFE5-4F6A-B6C7-B895BB01418A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{304F5DAA-B89D-4091-8861-1630C13CCDD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{304F5DAA-B89D-4091-8861-1630C13CCDD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Zuko" sheetId="1" r:id="rId1"/>
@@ -437,13 +437,13 @@
     <t>Mistveil Plains</t>
   </si>
   <si>
-    <t>Nita, Forum Concilliator</t>
-  </si>
-  <si>
     <t>Fields of Strife</t>
   </si>
   <si>
     <t>Forum of Amity</t>
+  </si>
+  <si>
+    <t>Nita, Forum Conciliator</t>
   </si>
 </sst>
 </file>
@@ -1233,10 +1233,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1248,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2479,10 +2479,10 @@
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D99" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F99" s="4">
         <v>3</v>

--- a/Decks/Zuko.xlsx
+++ b/Decks/Zuko.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE768CB8-DFE5-4F6A-B6C7-B895BB01418A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE22224-F25A-4F8B-AB79-E9FD189A54D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{304F5DAA-B89D-4091-8861-1630C13CCDD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{304F5DAA-B89D-4091-8861-1630C13CCDD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Zuko" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="133">
   <si>
     <t>Função</t>
   </si>
@@ -242,9 +242,6 @@
     <t>Exile</t>
   </si>
   <si>
-    <t>Cunning Rhetoric</t>
-  </si>
-  <si>
     <t>Commune with Lava</t>
   </si>
   <si>
@@ -344,9 +341,6 @@
     <t>The Last Agni Kai</t>
   </si>
   <si>
-    <t>Plargg and Nassari</t>
-  </si>
-  <si>
     <t>March of Reckless Joy</t>
   </si>
   <si>
@@ -356,9 +350,6 @@
     <t>Reconnaissance</t>
   </si>
   <si>
-    <t>Oracle's Vault</t>
-  </si>
-  <si>
     <t>Spikeshot Elder</t>
   </si>
   <si>
@@ -416,9 +407,6 @@
     <t>Ominous Asylum</t>
   </si>
   <si>
-    <t>Pile On</t>
-  </si>
-  <si>
     <t>Vanquish the Horde</t>
   </si>
   <si>
@@ -444,6 +432,9 @@
   </si>
   <si>
     <t>Nita, Forum Conciliator</t>
+  </si>
+  <si>
+    <t>Scuzzback Scrounger</t>
   </si>
 </sst>
 </file>
@@ -884,14 +875,14 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B64" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B65" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -918,10 +909,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -948,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -963,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -978,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -1008,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -1023,10 +1014,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1098,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
@@ -1116,7 +1107,7 @@
         <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1131,7 +1122,7 @@
         <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1146,7 +1137,7 @@
         <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1158,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
         <v>21</v>
@@ -1173,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1191,7 +1182,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1203,10 +1194,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1218,10 +1209,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1233,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1248,10 +1239,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1413,10 +1404,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F38" s="4">
         <v>3</v>
@@ -1431,10 +1422,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D39" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F39" s="4">
         <v>2</v>
@@ -1503,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F43" s="4">
         <v>3</v>
@@ -1575,10 +1566,10 @@
         <v>0</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F47" s="4">
         <v>3</v>
@@ -1665,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F52" s="4">
         <v>6</v>
@@ -1679,32 +1670,32 @@
         <v>33</v>
       </c>
       <c r="B53" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C53&lt;&gt;D53</f>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D53" t="s">
-        <v>37</v>
-      </c>
-      <c r="F53" s="4">
-        <v>4</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="D54" t="s">
-        <v>104</v>
+        <v>37</v>
+      </c>
+      <c r="F54" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1713,13 +1704,13 @@
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D55" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1730,11 +1721,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C56" t="s">
-        <v>39</v>
+      <c r="C56" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="D56" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1745,11 +1736,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>130</v>
+      <c r="C57" t="s">
+        <v>39</v>
       </c>
       <c r="D57" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1760,11 +1751,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C58" t="s">
-        <v>40</v>
+      <c r="C58" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="D58" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1775,11 +1766,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>41</v>
+      <c r="C59" t="s">
+        <v>40</v>
       </c>
       <c r="D59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -1788,13 +1779,13 @@
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -1803,13 +1794,13 @@
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -1821,10 +1812,10 @@
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D62" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -1833,13 +1824,13 @@
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="D63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -1848,28 +1839,28 @@
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="D64" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B65" s="5" t="b">
-        <f t="shared" ref="B65:B101" si="1">C65&lt;&gt;D65</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -1877,29 +1868,29 @@
         <v>48</v>
       </c>
       <c r="B66" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
+        <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D67" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -1911,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="D68" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -1923,13 +1914,13 @@
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="D69" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -1937,35 +1928,29 @@
         <v>50</v>
       </c>
       <c r="B70" s="5" t="b">
-        <f>C70&lt;&gt;D70</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D70" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B71" s="5" t="b">
         <f>C71&lt;&gt;D71</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D71" t="s">
-        <v>105</v>
-      </c>
-      <c r="E71" t="s">
-        <v>124</v>
-      </c>
-      <c r="F71" s="4">
-        <v>1</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -1974,16 +1959,19 @@
       </c>
       <c r="B72" s="5" t="b">
         <f>C72&lt;&gt;D72</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="D72" t="s">
-        <v>92</v>
+        <v>103</v>
+      </c>
+      <c r="E72" t="s">
+        <v>121</v>
       </c>
       <c r="F72" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -1991,17 +1979,17 @@
         <v>53</v>
       </c>
       <c r="B73" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C73&lt;&gt;D73</f>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="D73" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="F73" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2010,16 +1998,16 @@
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="D74" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F74" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2028,16 +2016,16 @@
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="D75" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F75" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2046,19 +2034,16 @@
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="D76" t="s">
-        <v>56</v>
-      </c>
-      <c r="E76" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="F76" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2067,16 +2052,19 @@
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>58</v>
+        <v>118</v>
+      </c>
+      <c r="D77" t="s">
+        <v>56</v>
+      </c>
+      <c r="E77" t="s">
+        <v>104</v>
       </c>
       <c r="F77" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2088,13 +2076,13 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D78" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="F78" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2106,13 +2094,13 @@
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>96</v>
+        <v>59</v>
+      </c>
+      <c r="D79" t="s">
+        <v>59</v>
       </c>
       <c r="F79" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D80" t="s">
-        <v>60</v>
+        <v>95</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="F80" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2142,13 +2130,13 @@
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D81" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F81" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2160,10 +2148,10 @@
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D82" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F82" s="4">
         <v>2</v>
@@ -2175,13 +2163,13 @@
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="D83" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F83" s="4">
         <v>2</v>
@@ -2189,20 +2177,20 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B84" s="5" t="b">
-        <f>C84&lt;&gt;D84</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D84" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F84" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -2214,13 +2202,13 @@
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="D85" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F85" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2228,17 +2216,17 @@
         <v>64</v>
       </c>
       <c r="B86" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>C86&lt;&gt;D86</f>
+        <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>65</v>
+        <v>92</v>
+      </c>
+      <c r="D86" t="s">
+        <v>92</v>
       </c>
       <c r="F86" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2247,37 +2235,34 @@
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D87" t="s">
-        <v>66</v>
+        <v>86</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="F87" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D88" t="s">
-        <v>94</v>
-      </c>
-      <c r="E88" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F88" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2285,20 +2270,20 @@
         <v>67</v>
       </c>
       <c r="B89" s="5" t="b">
-        <f>C89&lt;&gt;D89</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D89" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E89" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F89" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -2310,13 +2295,13 @@
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D90" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E90" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F90" s="4">
         <v>5</v>
@@ -2331,10 +2316,10 @@
         <v>1</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F91" s="4">
         <v>4</v>
@@ -2350,10 +2335,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D92" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F92" s="4">
         <v>3</v>
@@ -2369,10 +2354,10 @@
         <v>1</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F93" s="4">
         <v>3</v>
@@ -2387,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -2405,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F95" s="4">
         <v>4</v>
@@ -2423,10 +2408,10 @@
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F96" s="4">
         <v>3</v>
@@ -2442,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D97" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F97" s="4">
         <v>4</v>
@@ -2460,10 +2445,10 @@
         <v>1</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F98" s="4">
         <v>4</v>
@@ -2479,10 +2464,10 @@
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D99" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F99" s="4">
         <v>3</v>
@@ -2497,10 +2482,10 @@
         <v>1</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F100" s="4">
         <v>3</v>
@@ -2515,10 +2500,10 @@
         <v>1</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F101" s="4">
         <v>5</v>

--- a/Decks/Zuko.xlsx
+++ b/Decks/Zuko.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE22224-F25A-4F8B-AB79-E9FD189A54D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648E923F-E95E-47C0-BC9A-E12D5398ECD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{304F5DAA-B89D-4091-8861-1630C13CCDD9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="129">
   <si>
     <t>Função</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Terreno</t>
   </si>
   <si>
-    <t>Windbrisk Heights</t>
-  </si>
-  <si>
     <t>Pinnacle Monk</t>
   </si>
   <si>
@@ -173,15 +170,9 @@
     <t>Enter the Avatar State</t>
   </si>
   <si>
-    <t>Boon of Safety</t>
-  </si>
-  <si>
     <t>Ultimate Magic: Holy</t>
   </si>
   <si>
-    <t>Airbending Lesson</t>
-  </si>
-  <si>
     <t>Proteção</t>
   </si>
   <si>
@@ -263,9 +254,6 @@
     <t>Long-Range Sensor</t>
   </si>
   <si>
-    <t>Zuko, Exiled Prince</t>
-  </si>
-  <si>
     <t>Tavern Brawler</t>
   </si>
   <si>
@@ -278,9 +266,6 @@
     <t>Cait Sith, Fortune Teller</t>
   </si>
   <si>
-    <t>Commander Liara Portyr</t>
-  </si>
-  <si>
     <t>Bonehoard Dracosaur</t>
   </si>
   <si>
@@ -296,12 +281,6 @@
     <t>Valakut Exploration</t>
   </si>
   <si>
-    <t>Pack Rat</t>
-  </si>
-  <si>
-    <t>Mask of Avacyn</t>
-  </si>
-  <si>
     <t>Evolving Wilds</t>
   </si>
   <si>
@@ -326,18 +305,6 @@
     <t>Zuko's Conviction</t>
   </si>
   <si>
-    <t>Riveteers Overlook</t>
-  </si>
-  <si>
-    <t>Obscura Storefront</t>
-  </si>
-  <si>
-    <t>Emerge Unscathed</t>
-  </si>
-  <si>
-    <t>Mithril Coat</t>
-  </si>
-  <si>
     <t>The Last Agni Kai</t>
   </si>
   <si>
@@ -371,9 +338,6 @@
     <t>Cori Mountain Monastery</t>
   </si>
   <si>
-    <t>Terrain Generator</t>
-  </si>
-  <si>
     <t>Search the Premises</t>
   </si>
   <si>
@@ -392,15 +356,9 @@
     <t>Single Combat</t>
   </si>
   <si>
-    <t>Hot Soup</t>
-  </si>
-  <si>
     <t>Prowler's Helm</t>
   </si>
   <si>
-    <t>Makeshift Mannequin</t>
-  </si>
-  <si>
     <t>Journeyer's Kite</t>
   </si>
   <si>
@@ -410,18 +368,9 @@
     <t>Vanquish the Horde</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>Djeru and Hazoret</t>
-  </si>
-  <si>
     <t>Suspend Aggression</t>
   </si>
   <si>
-    <t>Advanced Reconstruction</t>
-  </si>
-  <si>
     <t>Mistveil Plains</t>
   </si>
   <si>
@@ -435,6 +384,45 @@
   </si>
   <si>
     <t>Scuzzback Scrounger</t>
+  </si>
+  <si>
+    <t>Scout's Warning</t>
+  </si>
+  <si>
+    <t>Axgard Armory</t>
+  </si>
+  <si>
+    <t>Big Apple, 3 a.m.</t>
+  </si>
+  <si>
+    <t>Fountainport</t>
+  </si>
+  <si>
+    <t>Kher Keep</t>
+  </si>
+  <si>
+    <t>Emerge Unschated</t>
+  </si>
+  <si>
+    <t>Obscura Stroyfront</t>
+  </si>
+  <si>
+    <t>Aranã, Heart of the Spider</t>
+  </si>
+  <si>
+    <t>Anzrag's Rampage</t>
+  </si>
+  <si>
+    <t>Agent 13, Sharon Carter</t>
+  </si>
+  <si>
+    <t>Tolls of War</t>
+  </si>
+  <si>
+    <t>Nico Minoru, Runaway</t>
+  </si>
+  <si>
+    <t>Court of Locthwain</t>
   </si>
 </sst>
 </file>
@@ -879,10 +867,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -894,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -909,10 +897,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -924,10 +912,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -936,13 +924,13 @@
       </c>
       <c r="B7" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -954,7 +942,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -966,10 +954,10 @@
       </c>
       <c r="B9" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -981,10 +969,10 @@
       </c>
       <c r="B10" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -996,13 +984,13 @@
       </c>
       <c r="B11" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1014,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1028,7 +1016,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" t="s">
         <v>16</v>
       </c>
       <c r="D13" t="s">
@@ -1071,10 +1059,10 @@
       </c>
       <c r="B16" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
@@ -1086,13 +1074,13 @@
       </c>
       <c r="B17" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1100,14 +1088,14 @@
         <v>8</v>
       </c>
       <c r="B18" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C18&lt;&gt;D18</f>
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,10 +1107,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1130,14 +1118,14 @@
         <v>8</v>
       </c>
       <c r="B20" s="5" t="b">
-        <f>C20&lt;&gt;D20</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1146,13 +1134,13 @@
       </c>
       <c r="B21" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1161,13 +1149,13 @@
       </c>
       <c r="B22" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1175,14 +1163,14 @@
         <v>8</v>
       </c>
       <c r="B23" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>C23&lt;&gt;D23</f>
+        <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1194,10 +1182,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1206,13 +1194,13 @@
       </c>
       <c r="B25" s="5" t="b">
         <f>C25&lt;&gt;D25</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1220,14 +1208,14 @@
         <v>8</v>
       </c>
       <c r="B26" s="5" t="b">
-        <f>C26&lt;&gt;D26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1235,14 +1223,14 @@
         <v>8</v>
       </c>
       <c r="B27" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C27&lt;&gt;D27</f>
+        <v>1</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1254,10 +1242,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1269,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1284,10 +1272,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1299,10 +1287,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1314,1168 +1302,1039 @@
         <v>0</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D35" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C33" s="4" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D36" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C34" s="4" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D37" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C35" s="4" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>24</v>
-      </c>
-      <c r="D35" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>25</v>
       </c>
       <c r="B38" s="5" t="b">
         <f>C38&lt;&gt;D38</f>
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
-      </c>
-      <c r="F38" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" s="5" t="b">
         <f>C39&lt;&gt;D39</f>
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>115</v>
-      </c>
-      <c r="F39" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C40" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C41" t="s">
         <v>26</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>26</v>
       </c>
-      <c r="F40" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>25</v>
-      </c>
-      <c r="B41" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C42" t="s">
         <v>27</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>27</v>
       </c>
-      <c r="F41" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>25</v>
-      </c>
-      <c r="B42" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C42" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" t="s">
-        <v>28</v>
-      </c>
-      <c r="F42" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B43" s="5" t="b">
         <f>C43&lt;&gt;D43</f>
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D43" t="s">
-        <v>82</v>
-      </c>
-      <c r="F43" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C45" t="s">
         <v>29</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>29</v>
       </c>
-      <c r="F44" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>25</v>
-      </c>
-      <c r="B45" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C45" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" t="s">
-        <v>30</v>
-      </c>
-      <c r="F45" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C47" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C48" t="s">
         <v>31</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D48" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>25</v>
-      </c>
-      <c r="B47" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C47" t="s">
-        <v>112</v>
-      </c>
-      <c r="D47" t="s">
-        <v>112</v>
-      </c>
-      <c r="F47" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>25</v>
-      </c>
-      <c r="B48" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C48" t="s">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>32</v>
       </c>
-      <c r="D48" t="s">
+      <c r="B49" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C49" t="s">
+        <v>33</v>
+      </c>
+      <c r="D49" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>32</v>
       </c>
-      <c r="F48" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>33</v>
-      </c>
-      <c r="B49" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B50" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C50" t="s">
         <v>34</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>34</v>
       </c>
-      <c r="F49" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>33</v>
-      </c>
-      <c r="B50" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C50" t="s">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>35</v>
       </c>
-      <c r="F50" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>33</v>
-      </c>
-      <c r="B51" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" t="s">
-        <v>36</v>
-      </c>
-      <c r="F51" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B52" s="5" t="b">
         <f>C52&lt;&gt;D52</f>
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D52" t="s">
-        <v>83</v>
-      </c>
-      <c r="F52" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B53" s="5" t="b">
         <f>C53&lt;&gt;D53</f>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D53" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>37</v>
       </c>
-      <c r="D54" t="s">
+      <c r="B55" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B56" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D56" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C57" t="s">
         <v>38</v>
       </c>
-      <c r="B55" s="5" t="b">
+      <c r="D57" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D58" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C59" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D60" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D61" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="5" t="b">
+        <f>C62&lt;&gt;D62</f>
+        <v>0</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D63" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D55" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D56" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C57" t="s">
-        <v>39</v>
-      </c>
-      <c r="D57" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D58" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C59" t="s">
-        <v>40</v>
-      </c>
-      <c r="D59" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D60" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D61" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C62" s="4" t="s">
+      <c r="C64" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D64" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D65" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C63" s="4" t="s">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>45</v>
-      </c>
-      <c r="D63" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D64" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D65" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>48</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D67" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>47</v>
+      </c>
+      <c r="B68" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>47</v>
+      </c>
+      <c r="B69" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D69" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>47</v>
+      </c>
+      <c r="B70" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D70" t="s">
         <v>49</v>
       </c>
-      <c r="D66" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>48</v>
-      </c>
-      <c r="B67" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D67" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>50</v>
-      </c>
-      <c r="B68" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D68" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>50</v>
-      </c>
-      <c r="B69" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D69" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>50</v>
-      </c>
-      <c r="B70" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D70" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B71" s="5" t="b">
         <f>C71&lt;&gt;D71</f>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D71" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B72" s="5" t="b">
         <f>C72&lt;&gt;D72</f>
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D72" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E72" t="s">
-        <v>121</v>
-      </c>
-      <c r="F72" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B73" s="5" t="b">
         <f>C73&lt;&gt;D73</f>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D73" t="s">
-        <v>91</v>
-      </c>
-      <c r="F73" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>50</v>
+      </c>
+      <c r="B74" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D74" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>50</v>
+      </c>
+      <c r="B75" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D75" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>50</v>
+      </c>
+      <c r="B76" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D76" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>50</v>
+      </c>
+      <c r="B77" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D77" t="s">
+        <v>127</v>
+      </c>
+      <c r="E77" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>50</v>
+      </c>
+      <c r="B78" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E78" t="s">
         <v>53</v>
       </c>
-      <c r="B74" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D74" t="s">
-        <v>38</v>
-      </c>
-      <c r="F74" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>53</v>
-      </c>
-      <c r="B75" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D75" t="s">
-        <v>54</v>
-      </c>
-      <c r="F75" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>53</v>
-      </c>
-      <c r="B76" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D76" t="s">
-        <v>55</v>
-      </c>
-      <c r="F76" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>53</v>
-      </c>
-      <c r="B77" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D77" t="s">
-        <v>56</v>
-      </c>
-      <c r="E77" t="s">
-        <v>104</v>
-      </c>
-      <c r="F77" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>53</v>
-      </c>
-      <c r="B78" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F78" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B79" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C79&lt;&gt;D79</f>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
-        <v>59</v>
-      </c>
-      <c r="F79" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B80" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C80&lt;&gt;D80</f>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F80" s="4">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="D80" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D81" t="s">
-        <v>60</v>
-      </c>
-      <c r="F81" s="4">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D82" t="s">
-        <v>61</v>
-      </c>
-      <c r="F82" s="4">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D83" t="s">
-        <v>62</v>
-      </c>
-      <c r="F83" s="4">
-        <v>2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D84" t="s">
-        <v>63</v>
-      </c>
-      <c r="F84" s="4">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B85" s="5" t="b">
         <f>C85&lt;&gt;D85</f>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D85" t="s">
-        <v>57</v>
-      </c>
-      <c r="F85" s="4">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B86" s="5" t="b">
         <f>C86&lt;&gt;D86</f>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D86" t="s">
-        <v>92</v>
-      </c>
-      <c r="F86" s="4">
-        <v>4</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F87" s="4">
-        <v>3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D88" t="s">
-        <v>66</v>
-      </c>
-      <c r="F88" s="4">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>64</v>
+      </c>
+      <c r="B89" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D89" t="s">
+        <v>86</v>
+      </c>
+      <c r="E89" t="s">
         <v>67</v>
-      </c>
-      <c r="B89" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D89" t="s">
-        <v>93</v>
-      </c>
-      <c r="E89" t="s">
-        <v>70</v>
-      </c>
-      <c r="F89" s="4">
-        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>73</v>
+      <c r="C90" t="s">
+        <v>70</v>
       </c>
       <c r="D90" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E90" t="s">
-        <v>101</v>
-      </c>
-      <c r="F90" s="4">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D91" t="s">
-        <v>69</v>
-      </c>
-      <c r="F91" s="4">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="I91" s="5"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D92" t="s">
-        <v>71</v>
-      </c>
-      <c r="F92" s="4">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="K92" s="5"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F93" s="4">
-        <v>3</v>
+        <v>128</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F95" s="4">
-        <v>4</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I95" s="5"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F96" s="4">
-        <v>3</v>
-      </c>
-      <c r="I96" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="D96" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D97" t="s">
-        <v>77</v>
-      </c>
-      <c r="F97" s="4">
-        <v>4</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H97" s="5"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B98" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>C98&lt;&gt;D98</f>
+        <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F98" s="4">
-        <v>4</v>
-      </c>
-      <c r="H98" s="5"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B99" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C99&lt;&gt;D99</f>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="D99" t="s">
-        <v>131</v>
-      </c>
-      <c r="F99" s="4">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2485,28 +2344,22 @@
         <v>80</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F100" s="4">
-        <v>3</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F101" s="4">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2527,7 +2380,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>C2:C101</xm:sqref>
+          <xm:sqref>C2:C12 C14:C89 C91:C101</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Decks/Zuko.xlsx
+++ b/Decks/Zuko.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648E923F-E95E-47C0-BC9A-E12D5398ECD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D055038B-70FC-4C12-83D9-666979CF2C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{304F5DAA-B89D-4091-8861-1630C13CCDD9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="128">
   <si>
     <t>Função</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>Terreno</t>
-  </si>
-  <si>
-    <t>Pinnacle Monk</t>
   </si>
   <si>
     <t>Rogue's Passage</t>
@@ -867,10 +864,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -882,10 +879,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -897,10 +894,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -912,10 +909,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -927,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -942,10 +939,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -957,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -972,10 +969,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -987,10 +984,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1002,10 +999,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1017,10 +1014,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1032,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1047,10 +1044,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1062,10 +1059,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1077,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1089,13 +1086,13 @@
       </c>
       <c r="B18" s="5" t="b">
         <f>C18&lt;&gt;D18</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1104,13 +1101,13 @@
       </c>
       <c r="B19" s="5" t="b">
         <f>C19&lt;&gt;D19</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,13 +1116,13 @@
       </c>
       <c r="B20" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1137,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1152,10 +1149,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1167,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1182,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1197,10 +1194,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1212,10 +1209,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1227,10 +1224,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1242,10 +1239,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1257,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1272,10 +1269,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1287,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1302,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1317,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1332,10 +1329,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1347,10 +1344,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1362,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1377,989 +1374,989 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" s="5" t="b">
         <f>C38&lt;&gt;D38</f>
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" s="5" t="b">
         <f>C39&lt;&gt;D39</f>
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C40" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C40" t="s">
-        <v>25</v>
-      </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B41" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B43" s="5" t="b">
         <f>C43&lt;&gt;D43</f>
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B45" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B47" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C49" t="s">
         <v>32</v>
       </c>
-      <c r="B49" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C49" t="s">
-        <v>33</v>
-      </c>
       <c r="D49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B52" s="5" t="b">
         <f>C52&lt;&gt;D52</f>
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B53" s="5" t="b">
         <f>C53&lt;&gt;D53</f>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D53" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>36</v>
+      </c>
+      <c r="B57" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C57" t="s">
         <v>37</v>
       </c>
-      <c r="B57" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C57" t="s">
-        <v>38</v>
-      </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D58" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D61" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B62" s="5" t="b">
         <f>C62&lt;&gt;D62</f>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>46</v>
+      </c>
+      <c r="B68" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B68" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="D68" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D70" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B71" s="5" t="b">
         <f>C71&lt;&gt;D71</f>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D71" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B72" s="5" t="b">
         <f>C72&lt;&gt;D72</f>
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B73" s="5" t="b">
         <f>C73&lt;&gt;D73</f>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D73" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>49</v>
+      </c>
+      <c r="B75" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D75" t="s">
         <v>50</v>
-      </c>
-      <c r="B75" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D75" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D76" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E78" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B79" s="5" t="b">
         <f>C79&lt;&gt;D79</f>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D79" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B80" s="5" t="b">
         <f>C80&lt;&gt;D80</f>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D81" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D82" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D83" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D84" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B85" s="5" t="b">
         <f>C85&lt;&gt;D85</f>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D85" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B86" s="5" t="b">
         <f>C86&lt;&gt;D86</f>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D86" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>60</v>
+      </c>
+      <c r="B87" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B87" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="D87" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D89" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E89" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E90" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D91" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I91" s="5"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D92" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K92" s="5"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>63</v>
+      </c>
+      <c r="B94" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B94" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="D94" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I95" s="5"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D96" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H97" s="5"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B98" s="5" t="b">
         <f>C98&lt;&gt;D98</f>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B99" s="5" t="b">
         <f>C99&lt;&gt;D99</f>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D99" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
